--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>79863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99036</v>
+        <v>99037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98930</v>
+        <v>98931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79863</v>
+        <v>79864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99037</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98931</v>
+        <v>98932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98932</v>
+        <v>98935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99041</v>
+        <v>99042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98935</v>
+        <v>98936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99042</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98936</v>
+        <v>98938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>131108336</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>131108336</v>
       </c>
       <c r="B7" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99045</v>
+        <v>99046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98939</v>
+        <v>98940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>131108336</v>
       </c>
       <c r="B7" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99046</v>
+        <v>99049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98940</v>
+        <v>98943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>131108336</v>
       </c>
       <c r="B7" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108233</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108290</v>
       </c>
       <c r="B3" t="n">
-        <v>99049</v>
+        <v>99050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131108129</v>
       </c>
       <c r="B4" t="n">
-        <v>98943</v>
+        <v>98944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131108130</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>131108289</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>131108336</v>
       </c>
       <c r="B7" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131108233</v>
+        <v>131108130</v>
       </c>
       <c r="B2" t="n">
-        <v>79873</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600829</v>
+        <v>600984</v>
       </c>
       <c r="R2" t="n">
-        <v>6975731</v>
+        <v>6975807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +740,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025-0312</t>
+          <t>2025-0320</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vanlig i området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,42 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131108290</v>
+        <v>131108289</v>
       </c>
       <c r="B3" t="n">
-        <v>99050</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600927</v>
+        <v>600832</v>
       </c>
       <c r="R3" t="n">
-        <v>6975752</v>
+        <v>6975715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2025-0321</t>
+          <t>2025-0314</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,42 +921,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131108129</v>
+        <v>131108233</v>
       </c>
       <c r="B4" t="n">
-        <v>98944</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600898</v>
+        <v>600829</v>
       </c>
       <c r="R4" t="n">
-        <v>6975748</v>
+        <v>6975731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +995,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025-0319</t>
+          <t>2025-0312</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131108130</v>
+        <v>131108336</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,34 +1057,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600984</v>
+        <v>600921</v>
       </c>
       <c r="R5" t="n">
-        <v>6975807</v>
+        <v>6975793</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-0320</t>
+          <t>2025-0318</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vanlig i området</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1155,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1171,42 +1166,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131108289</v>
+        <v>131108129</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600832</v>
+        <v>600898</v>
       </c>
       <c r="R6" t="n">
-        <v>6975715</v>
+        <v>6975748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1240,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-0314</t>
+          <t>2025-0319</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1260,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1296,37 +1291,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131108336</v>
+        <v>131108290</v>
       </c>
       <c r="B7" t="n">
-        <v>58051</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600921</v>
+        <v>600927</v>
       </c>
       <c r="R7" t="n">
-        <v>6975793</v>
+        <v>6975752</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-0318</t>
+          <t>2025-0321</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 31424-2025 artfynd.xlsx
+++ b/artfynd/A 31424-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108233</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1288,6 +1313,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108129</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1413,8 +1443,21 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>